--- a/import/WISI_products.xlsx
+++ b/import/WISI_products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive - University of East Anglia\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86592613-9E5B-42B4-946C-FC7440B7C09E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236622BC-5E2A-4546-AAFF-A593FF76777E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="160">
   <si>
     <t>Name</t>
   </si>
@@ -521,6 +521,9 @@
   </si>
   <si>
     <t>5…45 °C</t>
+  </si>
+  <si>
+    <t>WISI GF20128S.pdf</t>
   </si>
 </sst>
 </file>
@@ -1052,7 +1055,7 @@
         <v>100</v>
       </c>
       <c r="H3" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">

--- a/import/WISI_products.xlsx
+++ b/import/WISI_products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive - University of East Anglia\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236622BC-5E2A-4546-AAFF-A593FF76777E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7978FE-1B45-4C92-9C0E-1FC71A9A513F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Products" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="159">
   <si>
     <t>Name</t>
   </si>
@@ -76,18 +76,6 @@
     <t>Main-Category</t>
   </si>
   <si>
-    <t>Product Name</t>
-  </si>
-  <si>
-    <t>Specification</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>Right</t>
-  </si>
-  <si>
     <t>ip-streamer</t>
   </si>
   <si>
@@ -524,6 +512,15 @@
   </si>
   <si>
     <t>WISI GF20128S.pdf</t>
+  </si>
+  <si>
+    <t>tabName</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>Value</t>
   </si>
 </sst>
 </file>
@@ -641,10 +638,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{434A619D-1454-4BA0-9393-B4C2CD6704D4}" name="Table3" displayName="Table3" ref="A1:D1048576" totalsRowShown="0" dataCellStyle="Normal">
   <autoFilter ref="A1:D1048576" xr:uid="{434A619D-1454-4BA0-9393-B4C2CD6704D4}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{7B50757F-0F43-4B33-95FC-4895B729301E}" name="Product Name" dataCellStyle="Normal"/>
-    <tableColumn id="2" xr3:uid="{6D18D8FB-1AAC-4773-A378-03051750C873}" name="Specification" dataCellStyle="Normal"/>
-    <tableColumn id="3" xr3:uid="{4B535FD3-3DAB-49D1-B0B3-CED03E3BA218}" name="Left" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{D7449F3E-1EA4-40F7-BD92-F3B274E663ED}" name="Right" dataCellStyle="Normal"/>
+    <tableColumn id="1" xr3:uid="{7B50757F-0F43-4B33-95FC-4895B729301E}" name="ProductName" dataCellStyle="Normal"/>
+    <tableColumn id="2" xr3:uid="{6D18D8FB-1AAC-4773-A378-03051750C873}" name="tabName" dataCellStyle="Normal"/>
+    <tableColumn id="3" xr3:uid="{4B535FD3-3DAB-49D1-B0B3-CED03E3BA218}" name="Label" dataCellStyle="Normal"/>
+    <tableColumn id="4" xr3:uid="{D7449F3E-1EA4-40F7-BD92-F3B274E663ED}" name="Value" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1008,91 +1005,91 @@
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -1100,13 +1097,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -1114,7 +1111,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -1122,7 +1119,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -1130,7 +1127,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -1138,7 +1135,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -1146,7 +1143,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -1154,7 +1151,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -1162,7 +1159,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
@@ -1170,7 +1167,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -1178,7 +1175,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
@@ -1186,7 +1183,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F16" t="b">
         <v>0</v>
@@ -1194,7 +1191,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
@@ -1202,7 +1199,7 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F18" t="b">
         <v>0</v>
@@ -1210,7 +1207,7 @@
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F19" t="b">
         <v>0</v>
@@ -1218,7 +1215,7 @@
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -1226,7 +1223,7 @@
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
@@ -1234,7 +1231,7 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -1242,7 +1239,7 @@
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -1250,7 +1247,7 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -1258,7 +1255,7 @@
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
@@ -1266,7 +1263,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -1274,7 +1271,7 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1282,7 +1279,7 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -1290,7 +1287,7 @@
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -1298,7 +1295,7 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -1306,7 +1303,7 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -1314,7 +1311,7 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
@@ -1322,7 +1319,7 @@
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
@@ -1330,7 +1327,7 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
@@ -1338,7 +1335,7 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F35" t="b">
         <v>0</v>
@@ -1346,7 +1343,7 @@
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
@@ -1354,7 +1351,7 @@
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F37" t="b">
         <v>0</v>
@@ -1362,7 +1359,7 @@
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
@@ -1370,7 +1367,7 @@
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
@@ -1378,7 +1375,7 @@
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
@@ -1386,7 +1383,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F41" t="b">
         <v>0</v>
@@ -1394,7 +1391,7 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F42" t="b">
         <v>0</v>
@@ -1402,7 +1399,7 @@
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F43" t="b">
         <v>0</v>
@@ -1410,7 +1407,7 @@
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F44" t="b">
         <v>0</v>
@@ -1418,7 +1415,7 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -1426,7 +1423,7 @@
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F46" t="b">
         <v>0</v>
@@ -1434,7 +1431,7 @@
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -1442,7 +1439,7 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F48" t="b">
         <v>0</v>
@@ -1450,7 +1447,7 @@
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F49" t="b">
         <v>0</v>
@@ -1458,7 +1455,7 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
@@ -1466,7 +1463,7 @@
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F51" t="b">
         <v>0</v>
@@ -1474,7 +1471,7 @@
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
@@ -1482,7 +1479,7 @@
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
@@ -1490,7 +1487,7 @@
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
@@ -1498,7 +1495,7 @@
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F55" t="b">
         <v>0</v>
@@ -1506,7 +1503,7 @@
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
@@ -1514,7 +1511,7 @@
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F57" t="b">
         <v>0</v>
@@ -1522,7 +1519,7 @@
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F58" t="b">
         <v>0</v>
@@ -1530,7 +1527,7 @@
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F59" t="b">
         <v>0</v>
@@ -1975,226 +1972,226 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B20" t="s">
         <v>107</v>
-      </c>
-      <c r="B20" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B23" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2279,461 +2276,461 @@
   <sheetData>
     <row r="1" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s">
-        <v>31</v>
-      </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
         <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" t="s">
         <v>49</v>
-      </c>
-      <c r="C12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" t="s">
         <v>66</v>
-      </c>
-      <c r="C20" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D21" t="s">
         <v>66</v>
-      </c>
-      <c r="C21" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
         <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>77</v>
-      </c>
-      <c r="D24" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D28" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C32" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" t="s">
         <v>93</v>
-      </c>
-      <c r="D32" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D33">
         <v>76992</v>
@@ -2741,13 +2738,13 @@
     </row>
     <row r="34" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D34">
         <v>85176200</v>
@@ -2755,139 +2752,139 @@
     </row>
     <row r="35" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D35" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" t="s">
         <v>30</v>
-      </c>
-      <c r="C36" t="s">
-        <v>33</v>
-      </c>
-      <c r="D36" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D39" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D40" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C43" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" t="s">
+        <v>100</v>
+      </c>
+      <c r="C44" t="s">
         <v>99</v>
-      </c>
-      <c r="B44" t="s">
-        <v>104</v>
-      </c>
-      <c r="C44" t="s">
-        <v>103</v>
       </c>
       <c r="D44">
         <v>8</v>
@@ -2895,321 +2892,321 @@
     </row>
     <row r="45" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D45" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s">
+        <v>45</v>
+      </c>
+      <c r="C46" t="s">
+        <v>48</v>
+      </c>
+      <c r="D46" t="s">
         <v>49</v>
-      </c>
-      <c r="C46" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="47" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D48" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C49" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D49" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C50" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D50" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C51" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C52" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D52" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B53" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C53" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D53" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B54" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" t="s">
+        <v>65</v>
+      </c>
+      <c r="D54" t="s">
         <v>66</v>
-      </c>
-      <c r="C54" t="s">
-        <v>69</v>
-      </c>
-      <c r="D54" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B55" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" t="s">
+        <v>67</v>
+      </c>
+      <c r="D55" t="s">
         <v>66</v>
-      </c>
-      <c r="C55" t="s">
-        <v>71</v>
-      </c>
-      <c r="D55" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D56" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="57" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B57" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C57" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D57" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B58" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" t="s">
+        <v>73</v>
+      </c>
+      <c r="D58" t="s">
         <v>74</v>
-      </c>
-      <c r="C58" t="s">
-        <v>77</v>
-      </c>
-      <c r="D58" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="59" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B59" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C59" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D59" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B60" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C60" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D60" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C61" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D61" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="62" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B62" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C62" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D62" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B63" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C63" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D63" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B64" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D64" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B65" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C65" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D65" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B66" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C66" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D66" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B67" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C67" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D67">
         <v>76991</v>
@@ -3217,13 +3214,13 @@
     </row>
     <row r="68" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B68" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C68" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D68">
         <v>85176200</v>
@@ -3231,139 +3228,139 @@
     </row>
     <row r="69" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C69" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D69" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B70" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" t="s">
         <v>30</v>
-      </c>
-      <c r="C70" t="s">
-        <v>33</v>
-      </c>
-      <c r="D70" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="71" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C71" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D71" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C72" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D72" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="73" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D73" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D74" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="75" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B75" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C75" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D75" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="76" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C76" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D76" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B77" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C77" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D77" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="78" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B78" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C78" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D78">
         <v>8</v>
@@ -3371,489 +3368,489 @@
     </row>
     <row r="79" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B79" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C79" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D79" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B80" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C80" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D80" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B81" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C81" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D81" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="82" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B82" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C82" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D82" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B83" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C83" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D83" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="84" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B84" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C84" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D84" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B85" t="s">
+        <v>120</v>
+      </c>
+      <c r="C85" t="s">
         <v>124</v>
       </c>
-      <c r="C85" t="s">
-        <v>128</v>
-      </c>
       <c r="D85" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B86" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C86" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D86" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="87" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B87" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C87" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D87" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B88" t="s">
+        <v>126</v>
+      </c>
+      <c r="C88" t="s">
         <v>130</v>
       </c>
-      <c r="C88" t="s">
-        <v>134</v>
-      </c>
       <c r="D88" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="89" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C89" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D89" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="90" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B90" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C90" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D90" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B91" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C91" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D91" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B92" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C92" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D92" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="93" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B93" t="s">
+        <v>134</v>
+      </c>
+      <c r="C93" t="s">
+        <v>137</v>
+      </c>
+      <c r="D93" t="s">
         <v>138</v>
-      </c>
-      <c r="C93" t="s">
-        <v>141</v>
-      </c>
-      <c r="D93" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="94" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B94" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C94" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D94" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="95" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B95" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C95" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D95" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="96" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C96" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D96" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="97" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B97" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C97" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D97" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="98" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C98" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D98" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="99" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B99" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C99" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D99" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="100" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B100" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C100" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D100" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="101" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B101" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C101" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D101" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="102" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B102" t="s">
+        <v>62</v>
+      </c>
+      <c r="C102" t="s">
+        <v>67</v>
+      </c>
+      <c r="D102" t="s">
         <v>66</v>
-      </c>
-      <c r="C102" t="s">
-        <v>71</v>
-      </c>
-      <c r="D102" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="103" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B103" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C103" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D103" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="104" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C104" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D104" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="105" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B105" t="s">
+        <v>70</v>
+      </c>
+      <c r="C105" t="s">
+        <v>73</v>
+      </c>
+      <c r="D105" t="s">
         <v>74</v>
-      </c>
-      <c r="C105" t="s">
-        <v>77</v>
-      </c>
-      <c r="D105" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="106" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B106" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C106" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D106" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="107" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C107" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D107" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="108" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B108" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C108" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D108" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="109" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B109" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C109" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D109" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="110" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B110" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C110" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D110" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="111" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B111" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C111" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D111" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="112" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B112" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C112" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D112" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="113" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B113" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C113" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D113">
         <v>4010056768485</v>
@@ -3861,13 +3858,13 @@
     </row>
     <row r="114" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B114" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C114" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D114">
         <v>76960</v>
@@ -3875,13 +3872,13 @@
     </row>
     <row r="115" spans="1:4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B115" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C115" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D115">
         <v>85176299</v>

--- a/import/WISI_products.xlsx
+++ b/import/WISI_products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive - University of East Anglia\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F710451-C46B-42D6-B8DD-6FD3D43BB586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CECBA6-3861-4634-8054-D14155001A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="162">
   <si>
     <t>Name</t>
   </si>
@@ -530,6 +530,9 @@
   </si>
   <si>
     <t>power-supply</t>
+  </si>
+  <si>
+    <t>falcon</t>
   </si>
 </sst>
 </file>
@@ -571,7 +574,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -579,7 +582,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -1018,6 +1020,9 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
+      <c r="D2" t="s">
+        <v>161</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>141</v>
       </c>
@@ -1096,7 +1101,7 @@
       <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" t="s">
         <v>157</v>
       </c>
       <c r="F5" t="b">
@@ -3589,20 +3594,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="1b00f46c-3b5f-4331-86e9-781a15a27617" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="1b00f46c-3b5f-4331-86e9-781a15a27617" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3625,14 +3630,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C53BC2E-8A9E-4A85-93E8-958094667844}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA8B90F5-EBD9-46C8-A4AD-41D7B713BE29}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -3647,4 +3644,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C53BC2E-8A9E-4A85-93E8-958094667844}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/import/WISI_products.xlsx
+++ b/import/WISI_products.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive - University of East Anglia\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CECBA6-3861-4634-8054-D14155001A09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAFF5398-6121-4482-8669-50AC89511C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{45A4C8D8-9252-4E1C-B5EB-FB3ECB01B4B4}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="Specifications" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="OLE_LINK12" localSheetId="2">Specifications!$D$114</definedName>
+    <definedName name="OLE_LINK12" localSheetId="2">Specifications!$D$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="287">
   <si>
     <t>Name</t>
   </si>
@@ -94,33 +94,9 @@
     <t>Operating temperature range</t>
   </si>
   <si>
-    <t>Sales unit</t>
-  </si>
-  <si>
     <t>1 pcs.</t>
   </si>
   <si>
-    <t>Dimensions (WxHxD) sales unit</t>
-  </si>
-  <si>
-    <t>Packaging volume sales unit</t>
-  </si>
-  <si>
-    <t>Gross weight sales unit</t>
-  </si>
-  <si>
-    <t>EAN</t>
-  </si>
-  <si>
-    <t>Article number</t>
-  </si>
-  <si>
-    <t>Customs tariff number</t>
-  </si>
-  <si>
-    <t>Packaging Data</t>
-  </si>
-  <si>
     <t>tabName</t>
   </si>
   <si>
@@ -271,36 +247,6 @@
     <t>Software version</t>
   </si>
   <si>
-    <t>483 x 45 x 473 mm</t>
-  </si>
-  <si>
-    <t>10,3 dm³</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>Shipping unit</t>
-  </si>
-  <si>
-    <t>Dimensions (WxHxD) shipping unit</t>
-  </si>
-  <si>
-    <t>570 x 550 x 100 mm</t>
-  </si>
-  <si>
-    <t>Packaging volume shipping package</t>
-  </si>
-  <si>
-    <t>31.35 dm³</t>
-  </si>
-  <si>
-    <t>Gross weight shipping unit</t>
-  </si>
-  <si>
-    <t>8.04 kg</t>
-  </si>
-  <si>
     <t>GT10 0230</t>
   </si>
   <si>
@@ -410,15 +356,6 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>483 x 45 x 473 mm (1 RU, 19"-rack)</t>
-  </si>
-  <si>
-    <t>8,04 kg</t>
-  </si>
-  <si>
-    <t>31,35 dm³</t>
   </si>
   <si>
     <t>WISI Falcon.png</t>
@@ -533,13 +470,451 @@
   </si>
   <si>
     <t>falcon</t>
+  </si>
+  <si>
+    <t>GT 55 W 0230</t>
+  </si>
+  <si>
+    <t>WISI GT 55 W 0230.png</t>
+  </si>
+  <si>
+    <t>WISI GT 55 W 0230.pdf</t>
+  </si>
+  <si>
+    <t>With the optional power supply GT 55 W 0230 for 230 V AC, the reliability of the Tangram platform will be significantly increased - carrier grade. Thanks to the use of the optimised load sharing of redundant power supply, a permanent and reliable supply of the high density platform is guaranteed. During the operation, even in case of an error, the PSU can be changed without impairment of the customer signal. Furthermore, the PSU or the complete Tangram Platform can be integrated in a Performance Management Tool. For the PSU the most important parameters (internal, external output voltage, output current, temperature, type, serial number) can be transferred via SNMP.</t>
+  </si>
+  <si>
+    <t>Hot pluggable</t>
+  </si>
+  <si>
+    <t>Load sharing with redundant PSU</t>
+  </si>
+  <si>
+    <t>Information readable: type, serial number, hardware ID, software ID, max. output power, threshold of max. current, voltage and temperature</t>
+  </si>
+  <si>
+    <t>Measure values: output voltage internal, output voltage external, output current, temperature</t>
+  </si>
+  <si>
+    <t>Cold-device plug, IEC 60320-C14</t>
+  </si>
+  <si>
+    <t>DC-connetors</t>
+  </si>
+  <si>
+    <t>0 pcs.</t>
+  </si>
+  <si>
+    <t>Primary voltage</t>
+  </si>
+  <si>
+    <t>180...265 V AC</t>
+  </si>
+  <si>
+    <t>Frequency range</t>
+  </si>
+  <si>
+    <t>47...63 Hz</t>
+  </si>
+  <si>
+    <t>Secondary voltage</t>
+  </si>
+  <si>
+    <t>12 V DC</t>
+  </si>
+  <si>
+    <t>Power consumption</t>
+  </si>
+  <si>
+    <t>220 W</t>
+  </si>
+  <si>
+    <t>Efficiency</t>
+  </si>
+  <si>
+    <t>≥90 %</t>
+  </si>
+  <si>
+    <t>Protection class</t>
+  </si>
+  <si>
+    <t>IP30</t>
+  </si>
+  <si>
+    <t>Max. humidty (non-condensing)</t>
+  </si>
+  <si>
+    <t>EN 50083-2</t>
+  </si>
+  <si>
+    <t>Optopus</t>
+  </si>
+  <si>
+    <t>LX 50 0048</t>
+  </si>
+  <si>
+    <t>LX 50 0048.png</t>
+  </si>
+  <si>
+    <t>LX 50 0048.pdf</t>
+  </si>
+  <si>
+    <t>Tool less hot-swap modules, power supply units and fans</t>
+  </si>
+  <si>
+    <t>Mechanical backplate for optical and electrical connectors enables module exchange without recabeling.</t>
+  </si>
+  <si>
+    <t>Local and remote management</t>
+  </si>
+  <si>
+    <t>Fully redundant power supply concept</t>
+  </si>
+  <si>
+    <t>LX 50 0230</t>
+  </si>
+  <si>
+    <t>LX 50 0230.png</t>
+  </si>
+  <si>
+    <t>LX 50 0230.pdf</t>
+  </si>
+  <si>
+    <t>LX 50 0230 is a basic unit for the optical transmission platform Optopus, providing 14 module slots in 4 height units, with a supply voltage of 230 AC.</t>
+  </si>
+  <si>
+    <t>LX 50 0048 is a basic unit of the optical transmission platform Optopus, providing 14 module slots in a 4 RU chassis, powered from a 48 V DC mains supply.</t>
+  </si>
+  <si>
+    <t>LX 52</t>
+  </si>
+  <si>
+    <t>LX 52.pdf</t>
+  </si>
+  <si>
+    <t>LX 52.png</t>
+  </si>
+  <si>
+    <t>LX 52 is a base unit of the optical platform Optopus with 2 slots in a single rack unit chassis.</t>
+  </si>
+  <si>
+    <t>optical-transmitter</t>
+  </si>
+  <si>
+    <t>LX 11 S 200x</t>
+  </si>
+  <si>
+    <t>LX 11 S 200x.png</t>
+  </si>
+  <si>
+    <t>LX 11 S 200x.pdf</t>
+  </si>
+  <si>
+    <t>The LX 11 is part of the Optopus product portfolio. LX 11 is a single direct modulated fullband transmitter for use in HFC networks. The Optopus platform is a highly flexible and high density platform for all kinds of analog optical networks. The system is used in any network such as HFC, RF over Glass or RF Overlay in FTTX applications.</t>
+  </si>
+  <si>
+    <t>LX 11 S 200X</t>
+  </si>
+  <si>
+    <t>Adjustable OMI, Slope, NC-Input</t>
+  </si>
+  <si>
+    <t>Automatic level control (ALC)</t>
+  </si>
+  <si>
+    <t>Fullband transmitter 15...1218 MHz, Docsis 3.1 Ready</t>
+  </si>
+  <si>
+    <t>High RF Input Isolation</t>
+  </si>
+  <si>
+    <t>OMI Control Testport</t>
+  </si>
+  <si>
+    <t>SBS suppression</t>
+  </si>
+  <si>
+    <t>LX 12 S XX00</t>
+  </si>
+  <si>
+    <t>The LX 12 is part of the Optopus product portfolio. LX 12 is a dual direct modulated fullband transmitter with 2x 1310 nm for use in HFC networks.The Optopus platform is a highly flexible and high density platform for all kinds of analog optical networks. The system is used in any network such as HFC, RF over Glass or RF Overlay in FTTX applications.</t>
+  </si>
+  <si>
+    <t>Dual optical HFC transmitter for use in WISI Chassis LX 50</t>
+  </si>
+  <si>
+    <t>Dual Fullband transmitter 15...1218 MHz, Docsis 3.1 Ready</t>
+  </si>
+  <si>
+    <t>LX 13 S 0334</t>
+  </si>
+  <si>
+    <t>The LX 13 is part of the Optopus product portfolio. LX 13 is a dual CWDM upstream transmitter with two adjacent CWDM wavelengths for use in return path applications in HFC networks. The Optopus platform is a highly flexible and high density platform for all kinds of analog optical networks. The system is used in any network such as HFC, RF over Glass or RF Overlay in FTTX applications.</t>
+  </si>
+  <si>
+    <t>LX 13 S 0334.png</t>
+  </si>
+  <si>
+    <t>LX 13 S 0334.pdf</t>
+  </si>
+  <si>
+    <t>LX 15 S 120x</t>
+  </si>
+  <si>
+    <t>LX 15 S 120x.png</t>
+  </si>
+  <si>
+    <t>LX 12 S xx00</t>
+  </si>
+  <si>
+    <t>LX 15 S 120x.pdf</t>
+  </si>
+  <si>
+    <t>LX 12 S xx00.pdf</t>
+  </si>
+  <si>
+    <t>LX 12 S xx00.png</t>
+  </si>
+  <si>
+    <t>The LX 15 is part of the Optopus product portfolio. LX 15 is a direct modulated fullband transmitter with 1550 nm for use in RF Overlay and RFoG networks. The Optopus platform is a highly flexible and high density platform for all kinds of analog optical networks. The system is used in any network such as HFC, RF over Glass or RF Overlay in FTTX applications.</t>
+  </si>
+  <si>
+    <t>CWDM Up Stream Transmitter</t>
+  </si>
+  <si>
+    <t>High Density Dual CWDM-Transmitter</t>
+  </si>
+  <si>
+    <t>Two CWDM transmitter in one module</t>
+  </si>
+  <si>
+    <t>Highest performance with dual-stage isolator</t>
+  </si>
+  <si>
+    <t>Adjustable OMI</t>
+  </si>
+  <si>
+    <t>Electronic predistortion</t>
+  </si>
+  <si>
+    <t>LX 16 S 10xx</t>
+  </si>
+  <si>
+    <t>LX 16 S 10xx.png</t>
+  </si>
+  <si>
+    <t>LX 16 S 10xx.pdf</t>
+  </si>
+  <si>
+    <t>The LX 16 is part of the Optopus product portfolio. LX 16 is a cooled direct modulated DWDM upstream transmitter. The Optopus platform is a highly flexible and high density platform for all kinds of analog optical networks. The system is used in any network such as HFC, RF over Glass or RF Overlay in FTTX applications.</t>
+  </si>
+  <si>
+    <t>Temperature stabilized DFB laser</t>
+  </si>
+  <si>
+    <t>Hot Plug In/Out</t>
+  </si>
+  <si>
+    <t>Optical DWDM transmitter for use in WISI Chassis LX 50</t>
+  </si>
+  <si>
+    <t>Upstream transmitter 5...500 MHz</t>
+  </si>
+  <si>
+    <t>LX 18 S 1xxx</t>
+  </si>
+  <si>
+    <t>LX 18 S 1xxx.png</t>
+  </si>
+  <si>
+    <t>LX 18 S 1xxx.pdf</t>
+  </si>
+  <si>
+    <t>The LX 18 is part of the Optopus product portfolio. LX 18 is a direct modulated fullband dual transmitter with 1550 nm (DWDM). The Optopus platform is a highly flexible and high density platform for all kinds of analog optical networks. The system is used in any network such as HFC, RF over Glass or RF Overlay in FTTX applications.</t>
+  </si>
+  <si>
+    <t>High Density Dual Transmitter</t>
+  </si>
+  <si>
+    <t>SBS-Suppression</t>
+  </si>
+  <si>
+    <t>Dispersion compensation</t>
+  </si>
+  <si>
+    <t>No png</t>
+  </si>
+  <si>
+    <t>optical-receivers</t>
+  </si>
+  <si>
+    <t>LX 21 S 0100</t>
+  </si>
+  <si>
+    <t>LX 21 S 0100.png</t>
+  </si>
+  <si>
+    <t>LX 21 S 0100.pdf</t>
+  </si>
+  <si>
+    <t>The LX 21 is part of the Optopus product portfolio. LX 21 is an optical receiver for downstream applications with a wide input range. The Optopus is a highly flexible and high density platform for all kinds of analog optical networks. The system is used in any network such as HFC, RF over Glass or RF Overlay in FTTX applications.</t>
+  </si>
+  <si>
+    <t>Optical receiver for use in WISI Chassis LX50</t>
+  </si>
+  <si>
+    <t>Automatic Level Control (optical ALC) for constant RF-output level</t>
+  </si>
+  <si>
+    <t>LX 22 S 0400</t>
+  </si>
+  <si>
+    <t>LX 22 S 0400.png</t>
+  </si>
+  <si>
+    <t>LX 22 S 0400.pdf</t>
+  </si>
+  <si>
+    <t>The LX 22 is part of the Optopus product portfolio. LX 22 is a quattro upstream receiver for use in HFC networks. The Optopus platform is a highly flexible and high-density platform for all types of analog optical networks. The system is used in any network such as HFC, RF over Glass or RF Overlay in FTTX applications.</t>
+  </si>
+  <si>
+    <t>Optical quattro upstream receiver for use in WISI Chassis LX50</t>
+  </si>
+  <si>
+    <t>4 independent upstream channels per unit or ne combined output</t>
+  </si>
+  <si>
+    <t>4 RF output ports at rear</t>
+  </si>
+  <si>
+    <t>Optical automatic level control (ALC) for constant RF-Level</t>
+  </si>
+  <si>
+    <t>Redundancy switching option with LX71</t>
+  </si>
+  <si>
+    <t>LX 23 L 0431</t>
+  </si>
+  <si>
+    <t>LX 23 L 0431.png</t>
+  </si>
+  <si>
+    <t>LX 23 L 0431.pdf</t>
+  </si>
+  <si>
+    <t>The LX 23 is part of the Optopus product portfolio. LX 23 is a quattro upstream receiver for use in RFoG networks. The Optopus platform is a highly flexible and high density platform for all kinds of analog optical networks. The system is used in any network such as HFC, RF over Glass or RF Overlay in FTTX applications.</t>
+  </si>
+  <si>
+    <t>Optical quattro upstream receiver for use in WISI Chassis LX 50</t>
+  </si>
+  <si>
+    <t>4 independent upstream channels per unit or one combined output</t>
+  </si>
+  <si>
+    <t>Integrated RFoG-Filter (1310 nm)</t>
+  </si>
+  <si>
+    <t>IDS noise suppression (Squelch)</t>
+  </si>
+  <si>
+    <t>LX 22 H 0400</t>
+  </si>
+  <si>
+    <t>LX 22 H 0400.png</t>
+  </si>
+  <si>
+    <t>LX 22 H 0400.pdf</t>
+  </si>
+  <si>
+    <t>Optical quattro ultra low noise upstream receiver for use in WISI Chassis LX50</t>
+  </si>
+  <si>
+    <t>LX 30 S 1402</t>
+  </si>
+  <si>
+    <t>LX 30 S 1402.png</t>
+  </si>
+  <si>
+    <t>LX 30 S 1402.pdf</t>
+  </si>
+  <si>
+    <t>optical-amplifiers</t>
+  </si>
+  <si>
+    <t>The LX 30 is part of the Optopus product portfolio. LX 30 is an optical amplifier based on EDFA technology for use in FTTx and HFC networks. The Optopus platform is a highly flexible and high density platform for all kinds of analog optical networks. The system is used in any network such as HFC, RF over Glass or RF Overlay in FTTX applications.</t>
+  </si>
+  <si>
+    <t>Optical amplifier for use in WISI Chassis LX 50</t>
+  </si>
+  <si>
+    <t>Amplification of optical signals in the C-band</t>
+  </si>
+  <si>
+    <t>Up to four output ports with adjustable output power</t>
+  </si>
+  <si>
+    <t>Optical test port for the output signal</t>
+  </si>
+  <si>
+    <t>Wide input power range enables application as booster- or inline-amplifier</t>
+  </si>
+  <si>
+    <t>Low electrical power consumption</t>
+  </si>
+  <si>
+    <t>LX 30 S 1704</t>
+  </si>
+  <si>
+    <t>LX 30 S 1704.png</t>
+  </si>
+  <si>
+    <t>LX 30 S 1704.pdf</t>
+  </si>
+  <si>
+    <t>LX 30 S 2102</t>
+  </si>
+  <si>
+    <t>LX 30 S 2102.png</t>
+  </si>
+  <si>
+    <t>LX 30 S 2102.pdf</t>
+  </si>
+  <si>
+    <t>LX 32 L xxxx</t>
+  </si>
+  <si>
+    <t>LX 32 L xxxx.pdf</t>
+  </si>
+  <si>
+    <t>Optical Booster Amplifier for use in HFC and FTTx networks. Available with an different number of outputs, different output power and different types of connectors.</t>
+  </si>
+  <si>
+    <t>APC and AGC regulation</t>
+  </si>
+  <si>
+    <t>Integration in WISI Optopus system LX50</t>
+  </si>
+  <si>
+    <t>Extensive management via SNMP and HTTP</t>
+  </si>
+  <si>
+    <t>Closed module housing without fans</t>
+  </si>
+  <si>
+    <t>Optical test port for the output signal on the front</t>
+  </si>
+  <si>
+    <t>Low power consumption</t>
+  </si>
+  <si>
+    <t>LX 32 L xxxx.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -552,6 +927,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -574,7 +955,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -582,6 +963,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -614,8 +999,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{485EF06A-B474-447D-A8F9-89BDB6093278}" name="Table1" displayName="Table1" ref="A1:H175" totalsRowShown="0" headerRowDxfId="2" tableBorderDxfId="1" dataCellStyle="Normal">
-  <autoFilter ref="A1:H175" xr:uid="{485EF06A-B474-447D-A8F9-89BDB6093278}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{485EF06A-B474-447D-A8F9-89BDB6093278}" name="Table1" displayName="Table1" ref="A1:H170" totalsRowShown="0" headerRowDxfId="2" tableBorderDxfId="1" dataCellStyle="Normal">
+  <autoFilter ref="A1:H170" xr:uid="{485EF06A-B474-447D-A8F9-89BDB6093278}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{8B000398-16FD-4922-ADD1-EEFE78CEDB7B}" name="Name" dataCellStyle="Normal"/>
     <tableColumn id="2" xr3:uid="{479310F6-0875-4992-96FB-036B5871C710}" name="Brand" dataCellStyle="Normal"/>
@@ -642,8 +1027,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{434A619D-1454-4BA0-9393-B4C2CD6704D4}" name="Table3" displayName="Table3" ref="A1:D1048454" totalsRowShown="0" dataCellStyle="Normal">
-  <autoFilter ref="A1:D1048454" xr:uid="{434A619D-1454-4BA0-9393-B4C2CD6704D4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{434A619D-1454-4BA0-9393-B4C2CD6704D4}" name="Table3" displayName="Table3" ref="A1:D1048432" totalsRowShown="0" dataCellStyle="Normal">
+  <autoFilter ref="A1:D1048432" xr:uid="{434A619D-1454-4BA0-9393-B4C2CD6704D4}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{7B50757F-0F43-4B33-95FC-4895B729301E}" name="ProductName" dataCellStyle="Normal"/>
     <tableColumn id="2" xr3:uid="{6D18D8FB-1AAC-4773-A378-03051750C873}" name="tabName" dataCellStyle="Normal"/>
@@ -971,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20BB1523-B97F-467F-B1CE-C9963C8C7490}">
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.85546875" customWidth="1"/>
@@ -984,7 +1369,7 @@
     <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1010,7 +1395,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1021,318 +1406,630 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="H2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
       </c>
       <c r="G4" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="H4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="H5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s">
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="H6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>141</v>
+      </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>139</v>
+      </c>
+      <c r="E7" t="s">
+        <v>144</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>142</v>
+      </c>
+      <c r="H7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>167</v>
+      </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>166</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>178</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>168</v>
+      </c>
+      <c r="H8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>174</v>
+      </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>166</v>
       </c>
       <c r="D9" t="s">
-        <v>160</v>
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>177</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>179</v>
+      </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
+      <c r="C10" t="s">
+        <v>166</v>
+      </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>182</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H10" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>184</v>
+      </c>
       <c r="B11" t="s">
         <v>11</v>
       </c>
+      <c r="C11" t="s">
+        <v>166</v>
+      </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>183</v>
+      </c>
+      <c r="E11" t="s">
+        <v>187</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>185</v>
+      </c>
+      <c r="H11" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>205</v>
+      </c>
       <c r="B12" t="s">
         <v>11</v>
       </c>
+      <c r="C12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E12" t="s">
+        <v>196</v>
+      </c>
       <c r="F12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>208</v>
+      </c>
+      <c r="H12" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>199</v>
+      </c>
       <c r="B13" t="s">
         <v>11</v>
       </c>
+      <c r="C13" t="s">
+        <v>166</v>
+      </c>
+      <c r="D13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E13" t="s">
+        <v>200</v>
+      </c>
       <c r="F13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>201</v>
+      </c>
+      <c r="H13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>203</v>
+      </c>
       <c r="B14" t="s">
         <v>11</v>
       </c>
+      <c r="C14" t="s">
+        <v>166</v>
+      </c>
+      <c r="D14" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" t="s">
+        <v>209</v>
+      </c>
       <c r="F14" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>204</v>
+      </c>
+      <c r="H14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>216</v>
+      </c>
       <c r="B15" t="s">
         <v>11</v>
       </c>
+      <c r="C15" t="s">
+        <v>166</v>
+      </c>
+      <c r="D15" t="s">
+        <v>183</v>
+      </c>
+      <c r="E15" t="s">
+        <v>219</v>
+      </c>
       <c r="F15" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>217</v>
+      </c>
+      <c r="H15" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>224</v>
+      </c>
       <c r="B16" t="s">
         <v>11</v>
       </c>
+      <c r="C16" t="s">
+        <v>166</v>
+      </c>
+      <c r="D16" t="s">
+        <v>183</v>
+      </c>
+      <c r="E16" t="s">
+        <v>227</v>
+      </c>
       <c r="F16" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>225</v>
+      </c>
+      <c r="H16" t="s">
+        <v>226</v>
+      </c>
+      <c r="J16" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>233</v>
+      </c>
       <c r="B17" t="s">
         <v>11</v>
       </c>
+      <c r="C17" t="s">
+        <v>166</v>
+      </c>
+      <c r="D17" t="s">
+        <v>232</v>
+      </c>
+      <c r="E17" t="s">
+        <v>236</v>
+      </c>
       <c r="F17" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>234</v>
+      </c>
+      <c r="H17" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>239</v>
+      </c>
       <c r="B18" t="s">
         <v>11</v>
       </c>
+      <c r="C18" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" t="s">
+        <v>232</v>
+      </c>
+      <c r="E18" t="s">
+        <v>242</v>
+      </c>
       <c r="F18" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>240</v>
+      </c>
+      <c r="H18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>248</v>
+      </c>
       <c r="B19" t="s">
         <v>11</v>
       </c>
+      <c r="C19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" t="s">
+        <v>232</v>
+      </c>
+      <c r="E19" t="s">
+        <v>251</v>
+      </c>
       <c r="F19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>249</v>
+      </c>
+      <c r="H19" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>256</v>
+      </c>
       <c r="B20" t="s">
         <v>11</v>
       </c>
+      <c r="C20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D20" t="s">
+        <v>232</v>
+      </c>
+      <c r="E20" t="s">
+        <v>242</v>
+      </c>
       <c r="F20" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>257</v>
+      </c>
+      <c r="H20" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>260</v>
+      </c>
       <c r="B21" t="s">
         <v>11</v>
       </c>
+      <c r="C21" t="s">
+        <v>166</v>
+      </c>
+      <c r="D21" t="s">
+        <v>263</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>264</v>
+      </c>
       <c r="F21" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>261</v>
+      </c>
+      <c r="H21" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>271</v>
+      </c>
       <c r="B22" t="s">
         <v>11</v>
       </c>
+      <c r="C22" t="s">
+        <v>166</v>
+      </c>
+      <c r="D22" t="s">
+        <v>263</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>264</v>
+      </c>
       <c r="F22" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>272</v>
+      </c>
+      <c r="H22" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>274</v>
+      </c>
       <c r="B23" t="s">
         <v>11</v>
       </c>
+      <c r="C23" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" t="s">
+        <v>263</v>
+      </c>
+      <c r="E23" t="s">
+        <v>264</v>
+      </c>
       <c r="F23" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G23" t="s">
+        <v>275</v>
+      </c>
+      <c r="H23" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>277</v>
+      </c>
       <c r="B24" t="s">
         <v>11</v>
       </c>
+      <c r="C24" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" t="s">
+        <v>263</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>279</v>
+      </c>
       <c r="F24" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G24" t="s">
+        <v>286</v>
+      </c>
+      <c r="H24" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>11</v>
       </c>
+      <c r="C25" t="s">
+        <v>166</v>
+      </c>
       <c r="F25" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>11</v>
       </c>
+      <c r="C26" t="s">
+        <v>166</v>
+      </c>
       <c r="F26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>11</v>
       </c>
+      <c r="C27" t="s">
+        <v>166</v>
+      </c>
       <c r="F27" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>11</v>
       </c>
@@ -1340,7 +2037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>11</v>
       </c>
@@ -1348,7 +2045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>11</v>
       </c>
@@ -1356,7 +2053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>11</v>
       </c>
@@ -1364,7 +2061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>11</v>
       </c>
@@ -1517,41 +2214,26 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B51" t="s">
-        <v>11</v>
-      </c>
       <c r="F51" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
-        <v>11</v>
-      </c>
       <c r="F52" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B53" t="s">
-        <v>11</v>
-      </c>
       <c r="F53" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>11</v>
-      </c>
       <c r="F54" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B55" t="s">
-        <v>11</v>
-      </c>
       <c r="F55" t="b">
         <v>0</v>
       </c>
@@ -1938,31 +2620,6 @@
     </row>
     <row r="132" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F132" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F133" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F134" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F135" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F136" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F137" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1978,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F8B551A-BE85-4FE7-95EC-34C5D2DF628B}">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
@@ -1998,7 +2655,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2006,7 +2663,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2014,7 +2671,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2022,7 +2679,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2030,7 +2687,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2038,7 +2695,7 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2046,7 +2703,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2054,7 +2711,7 @@
         <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2062,7 +2719,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2070,7 +2727,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2078,7 +2735,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2086,7 +2743,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2094,7 +2751,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2102,315 +2759,1020 @@
         <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
         <v>31</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="B33" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="B34" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="B35" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="B36" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="B37" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="B38" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="B39" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="B40" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B41" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B42" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B43" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B44" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B46" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="B47" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="22.5" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>141</v>
+      </c>
+      <c r="B49" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>141</v>
+      </c>
+      <c r="B50" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>167</v>
+      </c>
+      <c r="B55" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>167</v>
+      </c>
+      <c r="B56" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>167</v>
+      </c>
+      <c r="B57" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>167</v>
+      </c>
+      <c r="B58" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B59" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B60" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B61" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B62" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>179</v>
+      </c>
+      <c r="B63" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>179</v>
+      </c>
+      <c r="B64" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>179</v>
+      </c>
+      <c r="B65" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>188</v>
+      </c>
+      <c r="B66" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>188</v>
+      </c>
+      <c r="B67" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>188</v>
+      </c>
+      <c r="B68" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>188</v>
+      </c>
+      <c r="B69" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>188</v>
+      </c>
+      <c r="B70" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>188</v>
+      </c>
+      <c r="B71" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>195</v>
+      </c>
+      <c r="B72" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>195</v>
+      </c>
+      <c r="B73" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>195</v>
+      </c>
+      <c r="B74" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>195</v>
+      </c>
+      <c r="B75" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>195</v>
+      </c>
+      <c r="B76" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>195</v>
+      </c>
+      <c r="B77" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>195</v>
+      </c>
+      <c r="B78" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>199</v>
+      </c>
+      <c r="B79" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>199</v>
+      </c>
+      <c r="B80" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>199</v>
+      </c>
+      <c r="B81" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>199</v>
+      </c>
+      <c r="B82" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>199</v>
+      </c>
+      <c r="B83" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>203</v>
+      </c>
+      <c r="B84" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>203</v>
+      </c>
+      <c r="B85" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>203</v>
+      </c>
+      <c r="B86" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>203</v>
+      </c>
+      <c r="B87" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>216</v>
+      </c>
+      <c r="B88" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>216</v>
+      </c>
+      <c r="B89" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>216</v>
+      </c>
+      <c r="B90" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>216</v>
+      </c>
+      <c r="B91" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>216</v>
+      </c>
+      <c r="B92" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>216</v>
+      </c>
+      <c r="B93" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>224</v>
+      </c>
+      <c r="B94" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>224</v>
+      </c>
+      <c r="B95" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>224</v>
+      </c>
+      <c r="B96" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>224</v>
+      </c>
+      <c r="B97" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>224</v>
+      </c>
+      <c r="B98" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>224</v>
+      </c>
+      <c r="B99" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>224</v>
+      </c>
+      <c r="B100" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>224</v>
+      </c>
+      <c r="B101" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>233</v>
+      </c>
+      <c r="B102" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>233</v>
+      </c>
+      <c r="B103" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>233</v>
+      </c>
+      <c r="B104" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>233</v>
+      </c>
+      <c r="B105" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>239</v>
+      </c>
+      <c r="B106" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>239</v>
+      </c>
+      <c r="B107" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>239</v>
+      </c>
+      <c r="B108" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>239</v>
+      </c>
+      <c r="B109" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>239</v>
+      </c>
+      <c r="B110" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>248</v>
+      </c>
+      <c r="B111" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>248</v>
+      </c>
+      <c r="B112" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>248</v>
+      </c>
+      <c r="B113" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>248</v>
+      </c>
+      <c r="B114" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>248</v>
+      </c>
+      <c r="B115" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>256</v>
+      </c>
+      <c r="B116" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>256</v>
+      </c>
+      <c r="B117" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>256</v>
+      </c>
+      <c r="B118" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>256</v>
+      </c>
+      <c r="B119" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>256</v>
+      </c>
+      <c r="B120" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>260</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>260</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>260</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>260</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>260</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>260</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>271</v>
+      </c>
+      <c r="B127" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>271</v>
+      </c>
+      <c r="B128" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>271</v>
+      </c>
+      <c r="B129" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>271</v>
+      </c>
+      <c r="B130" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>271</v>
+      </c>
+      <c r="B131" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>271</v>
+      </c>
+      <c r="B132" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>274</v>
+      </c>
+      <c r="B133" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>274</v>
+      </c>
+      <c r="B134" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>274</v>
+      </c>
+      <c r="B135" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>274</v>
+      </c>
+      <c r="B136" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>274</v>
+      </c>
+      <c r="B137" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>274</v>
+      </c>
+      <c r="B138" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>277</v>
+      </c>
+      <c r="B139" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>277</v>
+      </c>
+      <c r="B140" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>277</v>
+      </c>
+      <c r="B141" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>277</v>
+      </c>
+      <c r="B142" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>277</v>
+      </c>
+      <c r="B143" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>277</v>
+      </c>
+      <c r="B144" t="s">
+        <v>285</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2423,7 +3785,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8ACB312-7589-4E92-972B-4AEFAD0C5968}">
-  <dimension ref="A1:D841"/>
+  <dimension ref="A1:D819"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
@@ -2442,186 +3804,186 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -2630,18 +3992,18 @@
         <v>15</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D15">
         <v>0.95</v>
@@ -2649,41 +4011,41 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D18">
         <v>1010100</v>
@@ -2691,13 +4053,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D19">
         <v>3.5</v>
@@ -2705,657 +4067,517 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D25" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="D27" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28">
-        <v>4010056767624</v>
+        <v>88</v>
+      </c>
+      <c r="D28" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D29">
-        <v>76762</v>
+        <v>90</v>
+      </c>
+      <c r="D29" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" t="s">
-        <v>23</v>
-      </c>
-      <c r="D30">
-        <v>85176100</v>
+        <v>35</v>
+      </c>
+      <c r="D30" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
         <v>52</v>
       </c>
       <c r="D35" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="D37" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>14</v>
+      </c>
+      <c r="C38" t="s">
+        <v>57</v>
       </c>
       <c r="D38" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>108</v>
-      </c>
-      <c r="D40" t="s">
-        <v>109</v>
+        <v>60</v>
+      </c>
+      <c r="D40">
+        <v>0.95</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>14</v>
+      </c>
+      <c r="C41" t="s">
+        <v>61</v>
       </c>
       <c r="D41" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D43" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="D44" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="D45" t="s">
-        <v>116</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="D46" t="s">
-        <v>61</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="D47" t="s">
-        <v>61</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B48" t="s">
         <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>154</v>
       </c>
       <c r="D48" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
       </c>
       <c r="C49" t="s">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="D49" t="s">
-        <v>66</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="D50" t="s">
-        <v>67</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B51" t="s">
         <v>14</v>
       </c>
       <c r="C51" t="s">
-        <v>68</v>
-      </c>
-      <c r="D51">
-        <v>0.95</v>
+        <v>160</v>
+      </c>
+      <c r="D51" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B52" t="s">
         <v>14</v>
       </c>
       <c r="C52" t="s">
-        <v>69</v>
+        <v>162</v>
       </c>
       <c r="D52" t="s">
-        <v>72</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B53" t="s">
         <v>14</v>
       </c>
       <c r="C53" t="s">
-        <v>71</v>
-      </c>
-      <c r="D53" t="s">
-        <v>72</v>
+        <v>164</v>
+      </c>
+      <c r="D53">
+        <v>0.95</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B54" t="s">
         <v>14</v>
       </c>
       <c r="C54" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
       <c r="D54" t="s">
-        <v>119</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B55" t="s">
         <v>14</v>
       </c>
       <c r="C55" t="s">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="D55" t="s">
-        <v>121</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C56" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="D56" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>85</v>
-      </c>
-      <c r="B57" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" t="s">
-        <v>18</v>
-      </c>
-      <c r="D57" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>85</v>
-      </c>
-      <c r="B58" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" t="s">
-        <v>19</v>
-      </c>
-      <c r="D58" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>85</v>
-      </c>
-      <c r="B59" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" t="s">
-        <v>20</v>
-      </c>
-      <c r="D59" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>85</v>
-      </c>
-      <c r="B60" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" t="s">
-        <v>78</v>
-      </c>
-      <c r="D60" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>85</v>
-      </c>
-      <c r="B61" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" t="s">
-        <v>79</v>
-      </c>
-      <c r="D61" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>85</v>
-      </c>
-      <c r="B62" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" t="s">
-        <v>81</v>
-      </c>
-      <c r="D62" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>85</v>
-      </c>
-      <c r="B63" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" t="s">
-        <v>83</v>
-      </c>
-      <c r="D63" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>85</v>
-      </c>
-      <c r="B64" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" t="s">
-        <v>21</v>
-      </c>
-      <c r="D64">
-        <v>4010056768522</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>85</v>
-      </c>
-      <c r="B65" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" t="s">
-        <v>22</v>
-      </c>
-      <c r="D65">
-        <v>76919</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>85</v>
-      </c>
-      <c r="B66" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" t="s">
-        <v>23</v>
-      </c>
-      <c r="D66">
-        <v>85176100</v>
-      </c>
-    </row>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
